--- a/esthetician_forms/017_skin_care_consultation_request_form--esthetician_forms.xlsx
+++ b/esthetician_forms/017_skin_care_consultation_request_form--esthetician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'rosacea'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Rosacea'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'skin_cancer'}</t>
+          <t>skin_cancer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Skin Cancer'}</t>
+          <t>Skin Cancer</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'virtual_consultation'}</t>
+          <t>virtual_consultation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Virtual Consultation'}</t>
+          <t>Virtual Consultation</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'in-office_visit'}</t>
+          <t>in-office_visit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'In-Office Visit'}</t>
+          <t>In-Office Visit</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Phone Call'}</t>
+          <t>Phone Call</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
